--- a/public/tableau-e5.xlsx
+++ b/public/tableau-e5.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FBO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\val\BTS\perso\bloc1-presentation\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{63394734-9F53-4D2B-9FD4-8CE761F1C279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93718BDE-9040-4DBE-A55D-E0CD845187CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A26E744-21FE-4453-8B53-BA42E50DEBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29280" yWindow="480" windowWidth="27000" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
+    <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>Application Laravel</t>
+  </si>
+  <si>
+    <t>Création d'un E-Commerce</t>
+  </si>
+  <si>
+    <t>Janvier 2026 à Janvier 2026</t>
   </si>
 </sst>
 </file>
@@ -199,7 +205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -902,21 +908,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -950,29 +977,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1283,66 +1289,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="13.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="87.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="87.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.44140625" customWidth="1"/>
+    <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="48"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1">
-      <c r="A2" s="48" t="s">
+      <c r="H1" s="45"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="60" t="s">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="66" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="61"/>
-      <c r="H3" s="67"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="53"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="63" t="s">
+    <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1353,23 +1359,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A5" s="57" t="s">
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="59"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1">
-      <c r="A6" s="46" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="66"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="62" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1391,9 +1397,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1">
-      <c r="A7" s="47"/>
-      <c r="B7" s="56"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="55"/>
+      <c r="B7" s="63"/>
       <c r="C7" s="19" t="s">
         <v>18</v>
       </c>
@@ -1448,17 +1454,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.45">
-      <c r="A8" s="49" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="58"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1495,7 +1501,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>25</v>
       </c>
@@ -1548,7 +1554,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
@@ -1603,7 +1609,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>30</v>
       </c>
@@ -1650,7 +1656,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.6" customHeight="1">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>31</v>
       </c>
@@ -1699,7 +1705,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="40.15" customHeight="1">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
         <v>32</v>
       </c>
@@ -1752,7 +1758,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.6" customHeight="1">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
         <v>33</v>
       </c>
@@ -1805,7 +1811,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>34</v>
       </c>
@@ -1854,15 +1860,31 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="44"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="37"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1899,9 +1921,9 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -1944,7 +1966,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="14"/>
@@ -1989,17 +2011,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.45">
-      <c r="A19" s="52" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="54"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2036,14 +2058,16 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A20" s="45" t="s">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="22">
         <v>45546</v>
       </c>
-      <c r="C20" s="24"/>
+      <c r="C20" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="D20" s="26"/>
       <c r="E20" s="24"/>
       <c r="F20" s="28"/>
@@ -2085,14 +2109,16 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="45" t="s">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="22">
         <v>45546</v>
       </c>
-      <c r="C21" s="24"/>
+      <c r="C21" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="D21" s="24"/>
       <c r="E21" s="25"/>
       <c r="F21" s="28"/>
@@ -2134,7 +2160,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>38</v>
       </c>
@@ -2185,7 +2211,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>39</v>
       </c>
@@ -2197,7 +2223,9 @@
         <v>27</v>
       </c>
       <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="F23" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="G23" s="24"/>
       <c r="H23" s="37"/>
       <c r="I23"/>
@@ -2236,7 +2264,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>40</v>
       </c>
@@ -2289,7 +2317,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="14"/>
@@ -2334,7 +2362,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="14"/>
@@ -2379,17 +2407,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.45">
-      <c r="A27" s="52" t="s">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A27" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2426,7 +2454,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>43</v>
       </c>
@@ -2479,7 +2507,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="14"/>
@@ -2524,7 +2552,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="14"/>
@@ -2569,7 +2597,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="14"/>
@@ -2614,7 +2642,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="14"/>
@@ -2659,7 +2687,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="14"/>
@@ -2704,7 +2732,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="16"/>
@@ -2749,7 +2777,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.9">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2794,59 +2822,54 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1"/>
-    <row r="37" spans="1:43" customFormat="1"/>
-    <row r="38" spans="1:43" customFormat="1"/>
-    <row r="39" spans="1:43" customFormat="1"/>
-    <row r="40" spans="1:43" customFormat="1"/>
-    <row r="41" spans="1:43" customFormat="1"/>
-    <row r="42" spans="1:43" customFormat="1"/>
-    <row r="43" spans="1:43" customFormat="1"/>
-    <row r="44" spans="1:43" customFormat="1"/>
-    <row r="45" spans="1:43" customFormat="1"/>
-    <row r="46" spans="1:43" customFormat="1"/>
-    <row r="47" spans="1:43" customFormat="1"/>
-    <row r="48" spans="1:43" customFormat="1"/>
-    <row r="49" customFormat="1"/>
-    <row r="50" customFormat="1"/>
-    <row r="51" customFormat="1"/>
-    <row r="52" customFormat="1"/>
-    <row r="53" customFormat="1"/>
-    <row r="54" customFormat="1"/>
-    <row r="55" customFormat="1"/>
-    <row r="56" customFormat="1"/>
-    <row r="57" customFormat="1"/>
-    <row r="58" customFormat="1"/>
-    <row r="59" customFormat="1"/>
-    <row r="60" customFormat="1"/>
-    <row r="61" customFormat="1"/>
-    <row r="62" customFormat="1"/>
-    <row r="63" customFormat="1"/>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
-    <row r="70" customFormat="1"/>
-    <row r="71" customFormat="1"/>
-    <row r="72" customFormat="1"/>
-    <row r="73" customFormat="1"/>
-    <row r="74" customFormat="1"/>
-    <row r="75" customFormat="1"/>
-    <row r="76" customFormat="1"/>
-    <row r="77" customFormat="1"/>
-    <row r="78" customFormat="1"/>
-    <row r="79" customFormat="1"/>
-    <row r="80" customFormat="1"/>
-    <row r="81" customFormat="1"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2854,6 +2877,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2864,21 +2892,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD74F307FBE60B429D5B9E54272D49B2" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="484a37c26cc95603cc0eec74771f069c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="55930c89-10a9-47af-b496-ed7fca1744c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="19ae68a1085aa52266ad5cb0bc461ecf" ns2:_="">
     <xsd:import namespace="55930c89-10a9-47af-b496-ed7fca1744c0"/>
@@ -3022,14 +3035,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF504985-645B-4D2C-814C-C1A0AB864944}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DA38392-9E29-49DE-AF96-5B38C5609CFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="55930c89-10a9-47af-b496-ed7fca1744c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688D5EEF-EDE3-4672-AA8D-3EC315F9D437}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688D5EEF-EDE3-4672-AA8D-3EC315F9D437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DA38392-9E29-49DE-AF96-5B38C5609CFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF504985-645B-4D2C-814C-C1A0AB864944}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>